--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96665</v>
+        <v>96668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96668</v>
+        <v>96669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96669</v>
+        <v>96674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96674</v>
+        <v>96676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
